--- a/reports/orphan-donations.xlsx
+++ b/reports/orphan-donations.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:I82"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -410,30 +410,27 @@
         <v>PrayerId</v>
       </c>
       <c r="D1" t="str">
-        <v>SourceProjectName</v>
+        <v>Total</v>
       </c>
       <c r="E1" t="str">
-        <v>Total</v>
+        <v>ChargeCurrency</v>
       </c>
       <c r="F1" t="str">
-        <v>ChargeCurrency</v>
+        <v>DateCreated</v>
       </c>
       <c r="G1" t="str">
-        <v>DateCreated</v>
+        <v>PaymentMethod</v>
       </c>
       <c r="H1" t="str">
-        <v>PaymentMethod</v>
+        <v>OrphanReason</v>
       </c>
       <c r="I1" t="str">
-        <v>OrphanReason</v>
-      </c>
-      <c r="J1" t="str">
         <v>MigratedToItemId</v>
       </c>
     </row>
     <row r="2">
       <c r="A2">
-        <v>1349192</v>
+        <v>1</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -441,669 +438,2327 @@
       <c r="C2" t="str">
         <v/>
       </c>
-      <c r="D2" t="str">
-        <v>משפחת פרץ</v>
-      </c>
-      <c r="E2">
-        <v>174</v>
+      <c r="D2">
+        <v>345</v>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>Mon May 09 2016 19:38:42 GMT+0300 (שעון ישראל (קיץ))</v>
       </c>
       <c r="G2" t="str">
-        <v>2025-07-20 22:27:50</v>
+        <v>CreditCard</v>
       </c>
       <c r="H2" t="str">
-        <v>PayPal</v>
-      </c>
-      <c r="I2" t="str">
-        <v>project-not-migrated</v>
-      </c>
-      <c r="J2">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I2">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>1705565</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>12034</v>
+        <v>1</v>
       </c>
       <c r="C3" t="str">
         <v/>
       </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3">
-        <v>10</v>
+      <c r="D3">
+        <v>250</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Tue May 10 2016 13:57:44 GMT+0300 (שעון ישראל (קיץ))</v>
       </c>
       <c r="G3" t="str">
-        <v>2026-03-19 15:47:00</v>
+        <v>CreditCard</v>
       </c>
       <c r="H3" t="str">
-        <v>NedarimPlus</v>
-      </c>
-      <c r="I3" t="str">
-        <v>project-id-not-in-products (dangling)</v>
-      </c>
-      <c r="J3">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I3">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>1705578</v>
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>12034</v>
+        <v>1</v>
       </c>
       <c r="C4" t="str">
         <v/>
       </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
-      <c r="E4">
-        <v>10</v>
+      <c r="D4">
+        <v>230</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Tue May 10 2016 13:58:12 GMT+0300 (שעון ישראל (קיץ))</v>
       </c>
       <c r="G4" t="str">
-        <v>2026-03-19 16:00:00</v>
+        <v>PayPal</v>
       </c>
       <c r="H4" t="str">
-        <v>NedarimPlus</v>
-      </c>
-      <c r="I4" t="str">
-        <v>project-id-not-in-products (dangling)</v>
-      </c>
-      <c r="J4">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I4">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>1705586</v>
+        <v>4</v>
       </c>
       <c r="B5">
-        <v>12034</v>
+        <v>1</v>
       </c>
       <c r="C5" t="str">
         <v/>
       </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5">
-        <v>3</v>
+      <c r="D5">
+        <v>456</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Tue May 10 2016 14:21:26 GMT+0300 (שעון ישראל (קיץ))</v>
       </c>
       <c r="G5" t="str">
-        <v>2026-03-19 16:08:00</v>
+        <v>CreditCard</v>
       </c>
       <c r="H5" t="str">
-        <v>NedarimPlus</v>
-      </c>
-      <c r="I5" t="str">
-        <v>project-id-not-in-products (dangling)</v>
-      </c>
-      <c r="J5">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I5">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>1705588</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>12034</v>
+        <v>1</v>
       </c>
       <c r="C6" t="str">
         <v/>
       </c>
-      <c r="D6" t="str">
-        <v/>
-      </c>
-      <c r="E6">
-        <v>19</v>
+      <c r="D6">
+        <v>567</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Tue May 10 2016 14:21:42 GMT+0300 (שעון ישראל (קיץ))</v>
       </c>
       <c r="G6" t="str">
-        <v>2026-03-19 16:17:00</v>
+        <v>CreditCard</v>
       </c>
       <c r="H6" t="str">
-        <v>NedarimPlus</v>
-      </c>
-      <c r="I6" t="str">
-        <v>project-id-not-in-products (dangling)</v>
-      </c>
-      <c r="J6">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I6">
         <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>1705590</v>
+        <v>31</v>
       </c>
       <c r="B7">
-        <v>12034</v>
+        <v>1</v>
       </c>
       <c r="C7" t="str">
         <v/>
       </c>
-      <c r="D7" t="str">
-        <v/>
-      </c>
-      <c r="E7">
-        <v>5</v>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Wed Jul 27 2016 14:12:42 GMT+0300 (שעון ישראל (קיץ))</v>
       </c>
       <c r="G7" t="str">
-        <v>2026-03-19 16:22:00</v>
+        <v>CreditCard</v>
       </c>
       <c r="H7" t="str">
-        <v>NedarimPlus</v>
-      </c>
-      <c r="I7" t="str">
-        <v>project-id-not-in-products (dangling)</v>
-      </c>
-      <c r="J7">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I7">
         <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>1705617</v>
+        <v>48</v>
       </c>
       <c r="B8">
-        <v>12034</v>
+        <v>1</v>
       </c>
       <c r="C8" t="str">
         <v/>
       </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
-      <c r="E8">
-        <v>4</v>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Fri Aug 19 2016 04:25:23 GMT+0300 (שעון ישראל (קיץ))</v>
       </c>
       <c r="G8" t="str">
-        <v>2026-03-19 16:50:00</v>
+        <v>CreditCard</v>
       </c>
       <c r="H8" t="str">
-        <v>NedarimPlus</v>
-      </c>
-      <c r="I8" t="str">
-        <v>project-id-not-in-products (dangling)</v>
-      </c>
-      <c r="J8">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I8">
         <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>1705622</v>
+        <v>804763</v>
       </c>
       <c r="B9">
-        <v>12034</v>
+        <v>1057</v>
       </c>
       <c r="C9" t="str">
         <v/>
       </c>
-      <c r="D9" t="str">
-        <v/>
-      </c>
-      <c r="E9">
-        <v>18</v>
+      <c r="D9">
+        <v>72</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v>Tue Oct 10 2023 00:05:36 GMT+0300 (שעון ישראל (קיץ))</v>
       </c>
       <c r="G9" t="str">
-        <v>2026-03-19 16:59:00</v>
+        <v>CreditCard</v>
       </c>
       <c r="H9" t="str">
-        <v>NedarimPlus</v>
-      </c>
-      <c r="I9" t="str">
-        <v>project-id-not-in-products (dangling)</v>
-      </c>
-      <c r="J9">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I9">
         <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>1705623</v>
+        <v>804824</v>
       </c>
       <c r="B10">
-        <v>12034</v>
+        <v>1057</v>
       </c>
       <c r="C10" t="str">
         <v/>
       </c>
-      <c r="D10" t="str">
-        <v/>
-      </c>
-      <c r="E10">
-        <v>10</v>
+      <c r="D10">
+        <v>72</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v>Tue Oct 10 2023 00:36:05 GMT+0300 (שעון ישראל (קיץ))</v>
       </c>
       <c r="G10" t="str">
-        <v>2026-03-19 17:00:00</v>
+        <v>PayPal</v>
       </c>
       <c r="H10" t="str">
-        <v>NedarimPlus</v>
-      </c>
-      <c r="I10" t="str">
-        <v>project-id-not-in-products (dangling)</v>
-      </c>
-      <c r="J10">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I10">
         <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>1705634</v>
+        <v>804852</v>
       </c>
       <c r="B11">
-        <v>12034</v>
+        <v>1057</v>
       </c>
       <c r="C11" t="str">
         <v/>
       </c>
-      <c r="D11" t="str">
-        <v/>
-      </c>
-      <c r="E11">
-        <v>5</v>
+      <c r="D11">
+        <v>40</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v>Tue Oct 10 2023 00:54:03 GMT+0300 (שעון ישראל (קיץ))</v>
       </c>
       <c r="G11" t="str">
-        <v>2026-03-19 17:11:00</v>
+        <v>CreditCard</v>
       </c>
       <c r="H11" t="str">
-        <v>NedarimPlus</v>
-      </c>
-      <c r="I11" t="str">
-        <v>project-id-not-in-products (dangling)</v>
-      </c>
-      <c r="J11">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I11">
         <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>1705690</v>
+        <v>804878</v>
       </c>
       <c r="B12">
-        <v>12034</v>
+        <v>1057</v>
       </c>
       <c r="C12" t="str">
         <v/>
       </c>
-      <c r="D12" t="str">
-        <v/>
-      </c>
-      <c r="E12">
-        <v>3</v>
+      <c r="D12">
+        <v>72</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v>Tue Oct 10 2023 01:09:59 GMT+0300 (שעון ישראל (קיץ))</v>
       </c>
       <c r="G12" t="str">
-        <v>2026-03-19 17:55:00</v>
+        <v>CreditCard</v>
       </c>
       <c r="H12" t="str">
-        <v>NedarimPlus</v>
-      </c>
-      <c r="I12" t="str">
-        <v>project-id-not-in-products (dangling)</v>
-      </c>
-      <c r="J12">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I12">
         <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>1705800</v>
+        <v>804912</v>
       </c>
       <c r="B13">
-        <v>12034</v>
+        <v>1057</v>
       </c>
       <c r="C13" t="str">
         <v/>
       </c>
-      <c r="D13" t="str">
-        <v/>
-      </c>
-      <c r="E13">
-        <v>5</v>
+      <c r="D13">
+        <v>72</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v>Tue Oct 10 2023 01:34:56 GMT+0300 (שעון ישראל (קיץ))</v>
       </c>
       <c r="G13" t="str">
-        <v>2026-03-19 19:31:00</v>
+        <v>CreditCard</v>
       </c>
       <c r="H13" t="str">
-        <v>NedarimPlus</v>
-      </c>
-      <c r="I13" t="str">
-        <v>project-id-not-in-products (dangling)</v>
-      </c>
-      <c r="J13">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I13">
         <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>1705801</v>
+        <v>804943</v>
       </c>
       <c r="B14">
-        <v>12034</v>
+        <v>1057</v>
       </c>
       <c r="C14" t="str">
         <v/>
       </c>
-      <c r="D14" t="str">
-        <v/>
-      </c>
-      <c r="E14">
-        <v>50</v>
+      <c r="D14">
+        <v>72</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v>Tue Oct 10 2023 01:56:34 GMT+0300 (שעון ישראל (קיץ))</v>
       </c>
       <c r="G14" t="str">
-        <v>2026-03-19 19:31:00</v>
+        <v>CreditCard</v>
       </c>
       <c r="H14" t="str">
-        <v>NedarimPlus</v>
-      </c>
-      <c r="I14" t="str">
-        <v>project-id-not-in-products (dangling)</v>
-      </c>
-      <c r="J14">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I14">
         <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>1629198</v>
+        <v>804955</v>
       </c>
       <c r="B15">
-        <v>22488</v>
+        <v>1057</v>
       </c>
       <c r="C15" t="str">
         <v/>
       </c>
-      <c r="D15" t="str">
-        <v/>
-      </c>
-      <c r="E15">
-        <v>20</v>
+      <c r="D15">
+        <v>26</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v>Tue Oct 10 2023 02:04:17 GMT+0300 (שעון ישראל (קיץ))</v>
       </c>
       <c r="G15" t="str">
-        <v>2026-02-11 20:01:00</v>
+        <v>CreditCard</v>
       </c>
       <c r="H15" t="str">
-        <v>NedarimPlus</v>
-      </c>
-      <c r="I15" t="str">
-        <v>project-id-not-in-products (dangling)</v>
-      </c>
-      <c r="J15">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I15">
         <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>1629206</v>
+        <v>804965</v>
       </c>
       <c r="B16">
-        <v>22488</v>
+        <v>1057</v>
       </c>
       <c r="C16" t="str">
         <v/>
       </c>
-      <c r="D16" t="str">
-        <v/>
-      </c>
-      <c r="E16">
-        <v>100</v>
+      <c r="D16">
+        <v>18</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v>Tue Oct 10 2023 02:13:59 GMT+0300 (שעון ישראל (קיץ))</v>
       </c>
       <c r="G16" t="str">
-        <v>2026-02-11 20:14:00</v>
+        <v>PayPal</v>
       </c>
       <c r="H16" t="str">
-        <v>NedarimPlus</v>
-      </c>
-      <c r="I16" t="str">
-        <v>project-id-not-in-products (dangling)</v>
-      </c>
-      <c r="J16">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I16">
         <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>1629216</v>
+        <v>804968</v>
       </c>
       <c r="B17">
-        <v>22488</v>
+        <v>1057</v>
       </c>
       <c r="C17" t="str">
         <v/>
       </c>
-      <c r="D17" t="str">
-        <v/>
-      </c>
-      <c r="E17">
-        <v>18</v>
+      <c r="D17">
+        <v>26</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v>Tue Oct 10 2023 02:17:39 GMT+0300 (שעון ישראל (קיץ))</v>
       </c>
       <c r="G17" t="str">
-        <v>2026-02-11 20:22:00</v>
+        <v>PayPal</v>
       </c>
       <c r="H17" t="str">
-        <v>NedarimPlus</v>
-      </c>
-      <c r="I17" t="str">
-        <v>project-id-not-in-products (dangling)</v>
-      </c>
-      <c r="J17">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I17">
         <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>1629226</v>
+        <v>804969</v>
       </c>
       <c r="B18">
-        <v>22488</v>
+        <v>1057</v>
       </c>
       <c r="C18" t="str">
         <v/>
       </c>
-      <c r="D18" t="str">
-        <v/>
-      </c>
-      <c r="E18">
-        <v>50</v>
+      <c r="D18">
+        <v>26</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v>Tue Oct 10 2023 02:18:52 GMT+0300 (שעון ישראל (קיץ))</v>
       </c>
       <c r="G18" t="str">
-        <v>2026-02-11 20:30:00</v>
+        <v>PayPal</v>
       </c>
       <c r="H18" t="str">
-        <v>NedarimPlus</v>
-      </c>
-      <c r="I18" t="str">
-        <v>project-id-not-in-products (dangling)</v>
-      </c>
-      <c r="J18">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I18">
         <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>1629231</v>
+        <v>805001</v>
       </c>
       <c r="B19">
-        <v>22488</v>
+        <v>1057</v>
       </c>
       <c r="C19" t="str">
         <v/>
       </c>
-      <c r="D19" t="str">
-        <v/>
-      </c>
-      <c r="E19">
-        <v>936</v>
+      <c r="D19">
+        <v>72</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v>Tue Oct 10 2023 02:36:41 GMT+0300 (שעון ישראל (קיץ))</v>
       </c>
       <c r="G19" t="str">
-        <v>2026-02-11 20:36:00</v>
+        <v>PayPal</v>
       </c>
       <c r="H19" t="str">
-        <v>NedarimPlus</v>
-      </c>
-      <c r="I19" t="str">
-        <v>project-id-not-in-products (dangling)</v>
-      </c>
-      <c r="J19">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I19">
         <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>1629234</v>
+        <v>805010</v>
       </c>
       <c r="B20">
-        <v>22488</v>
+        <v>1057</v>
       </c>
       <c r="C20" t="str">
         <v/>
       </c>
-      <c r="D20" t="str">
-        <v/>
-      </c>
-      <c r="E20">
-        <v>20</v>
+      <c r="D20">
+        <v>72</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v>Tue Oct 10 2023 02:38:37 GMT+0300 (שעון ישראל (קיץ))</v>
       </c>
       <c r="G20" t="str">
-        <v>2026-02-11 20:44:00</v>
+        <v>CreditCard</v>
       </c>
       <c r="H20" t="str">
-        <v>NedarimPlus</v>
-      </c>
-      <c r="I20" t="str">
-        <v>project-id-not-in-products (dangling)</v>
-      </c>
-      <c r="J20">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I20">
         <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>1629247</v>
+        <v>805022</v>
       </c>
       <c r="B21">
-        <v>22488</v>
+        <v>1057</v>
       </c>
       <c r="C21" t="str">
         <v/>
       </c>
-      <c r="D21" t="str">
-        <v/>
-      </c>
-      <c r="E21">
-        <v>600</v>
+      <c r="D21">
+        <v>50</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v>Tue Oct 10 2023 02:49:34 GMT+0300 (שעון ישראל (קיץ))</v>
       </c>
       <c r="G21" t="str">
-        <v>2026-02-11 20:51:00</v>
+        <v>PayPal</v>
       </c>
       <c r="H21" t="str">
-        <v>NedarimPlus</v>
-      </c>
-      <c r="I21" t="str">
-        <v>project-id-not-in-products (dangling)</v>
-      </c>
-      <c r="J21">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I21">
         <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>1629250</v>
+        <v>805038</v>
       </c>
       <c r="B22">
-        <v>22488</v>
+        <v>1057</v>
       </c>
       <c r="C22" t="str">
         <v/>
       </c>
-      <c r="D22" t="str">
-        <v/>
-      </c>
-      <c r="E22">
-        <v>5</v>
+      <c r="D22">
+        <v>26</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v>Tue Oct 10 2023 02:58:34 GMT+0300 (שעון ישראל (קיץ))</v>
       </c>
       <c r="G22" t="str">
-        <v>2026-02-11 20:55:00</v>
+        <v>PayPal</v>
       </c>
       <c r="H22" t="str">
-        <v>NedarimPlus</v>
-      </c>
-      <c r="I22" t="str">
-        <v>project-id-not-in-products (dangling)</v>
-      </c>
-      <c r="J22">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I22">
         <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>1629260</v>
+        <v>805042</v>
       </c>
       <c r="B23">
-        <v>22488</v>
+        <v>1057</v>
       </c>
       <c r="C23" t="str">
         <v/>
       </c>
-      <c r="D23" t="str">
-        <v/>
-      </c>
-      <c r="E23">
+      <c r="D23">
         <v>50</v>
       </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v>Tue Oct 10 2023 03:02:03 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
       <c r="G23" t="str">
-        <v>2026-02-11 21:05:00</v>
+        <v>CreditCard</v>
       </c>
       <c r="H23" t="str">
-        <v>NedarimPlus</v>
-      </c>
-      <c r="I23" t="str">
-        <v>project-id-not-in-products (dangling)</v>
-      </c>
-      <c r="J23">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I23">
         <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>1629261</v>
+        <v>805055</v>
       </c>
       <c r="B24">
-        <v>22488</v>
+        <v>1057</v>
       </c>
       <c r="C24" t="str">
         <v/>
       </c>
-      <c r="D24" t="str">
-        <v/>
-      </c>
-      <c r="E24">
-        <v>25</v>
+      <c r="D24">
+        <v>18</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v>Tue Oct 10 2023 03:07:20 GMT+0300 (שעון ישראל (קיץ))</v>
       </c>
       <c r="G24" t="str">
-        <v>2026-02-11 21:06:00</v>
+        <v>CreditCard</v>
       </c>
       <c r="H24" t="str">
-        <v>NedarimPlus</v>
-      </c>
-      <c r="I24" t="str">
-        <v>project-id-not-in-products (dangling)</v>
-      </c>
-      <c r="J24">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>805063</v>
+      </c>
+      <c r="B25">
+        <v>1057</v>
+      </c>
+      <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="D25">
+        <v>72</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v>Tue Oct 10 2023 03:23:50 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G25" t="str">
+        <v>PayPal</v>
+      </c>
+      <c r="H25" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>805079</v>
+      </c>
+      <c r="B26">
+        <v>1057</v>
+      </c>
+      <c r="C26" t="str">
+        <v/>
+      </c>
+      <c r="D26">
+        <v>100</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v>Tue Oct 10 2023 03:44:27 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G26" t="str">
+        <v>PayPal</v>
+      </c>
+      <c r="H26" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>805095</v>
+      </c>
+      <c r="B27">
+        <v>1057</v>
+      </c>
+      <c r="C27" t="str">
+        <v/>
+      </c>
+      <c r="D27">
+        <v>26</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v>Tue Oct 10 2023 04:09:42 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G27" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H27" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>805116</v>
+      </c>
+      <c r="B28">
+        <v>1057</v>
+      </c>
+      <c r="C28" t="str">
+        <v/>
+      </c>
+      <c r="D28">
+        <v>72</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v>Tue Oct 10 2023 05:04:35 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G28" t="str">
+        <v>PayPal</v>
+      </c>
+      <c r="H28" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>805127</v>
+      </c>
+      <c r="B29">
+        <v>1057</v>
+      </c>
+      <c r="C29" t="str">
+        <v/>
+      </c>
+      <c r="D29">
+        <v>52</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v>Tue Oct 10 2023 05:39:21 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G29" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H29" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>805335</v>
+      </c>
+      <c r="B30">
+        <v>1057</v>
+      </c>
+      <c r="C30" t="str">
+        <v/>
+      </c>
+      <c r="D30">
+        <v>250</v>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v>Tue Oct 10 2023 14:02:03 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G30" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H30" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>805343</v>
+      </c>
+      <c r="B31">
+        <v>1057</v>
+      </c>
+      <c r="C31" t="str">
+        <v/>
+      </c>
+      <c r="D31">
+        <v>18</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v>Tue Oct 10 2023 14:11:06 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G31" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H31" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>805395</v>
+      </c>
+      <c r="B32">
+        <v>1057</v>
+      </c>
+      <c r="C32" t="str">
+        <v/>
+      </c>
+      <c r="D32">
+        <v>72</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v>Tue Oct 10 2023 15:10:17 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G32" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H32" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>805415</v>
+      </c>
+      <c r="B33">
+        <v>1057</v>
+      </c>
+      <c r="C33" t="str">
+        <v/>
+      </c>
+      <c r="D33">
+        <v>72</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v>Tue Oct 10 2023 15:36:28 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G33" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H33" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>805480</v>
+      </c>
+      <c r="B34">
+        <v>1057</v>
+      </c>
+      <c r="C34" t="str">
+        <v/>
+      </c>
+      <c r="D34">
+        <v>50</v>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v>Tue Oct 10 2023 16:30:32 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G34" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H34" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>805516</v>
+      </c>
+      <c r="B35">
+        <v>1057</v>
+      </c>
+      <c r="C35" t="str">
+        <v/>
+      </c>
+      <c r="D35">
+        <v>50</v>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v>Tue Oct 10 2023 17:03:20 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G35" t="str">
+        <v>PayPal</v>
+      </c>
+      <c r="H35" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>805689</v>
+      </c>
+      <c r="B36">
+        <v>1057</v>
+      </c>
+      <c r="C36" t="str">
+        <v/>
+      </c>
+      <c r="D36">
+        <v>72</v>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v>Tue Oct 10 2023 19:31:15 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G36" t="str">
+        <v>PayPal</v>
+      </c>
+      <c r="H36" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>805776</v>
+      </c>
+      <c r="B37">
+        <v>1057</v>
+      </c>
+      <c r="C37" t="str">
+        <v/>
+      </c>
+      <c r="D37">
+        <v>250</v>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v>Tue Oct 10 2023 20:02:38 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G37" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H37" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>806000</v>
+      </c>
+      <c r="B38">
+        <v>1057</v>
+      </c>
+      <c r="C38" t="str">
+        <v/>
+      </c>
+      <c r="D38">
+        <v>26</v>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v>Tue Oct 10 2023 22:29:50 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G38" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H38" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>806011</v>
+      </c>
+      <c r="B39">
+        <v>1057</v>
+      </c>
+      <c r="C39" t="str">
+        <v/>
+      </c>
+      <c r="D39">
+        <v>26</v>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v>Tue Oct 10 2023 22:36:16 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G39" t="str">
+        <v>PayPal</v>
+      </c>
+      <c r="H39" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>806032</v>
+      </c>
+      <c r="B40">
+        <v>1057</v>
+      </c>
+      <c r="C40" t="str">
+        <v/>
+      </c>
+      <c r="D40">
+        <v>260</v>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v>Tue Oct 10 2023 22:52:49 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G40" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H40" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>806113</v>
+      </c>
+      <c r="B41">
+        <v>1057</v>
+      </c>
+      <c r="C41" t="str">
+        <v/>
+      </c>
+      <c r="D41">
+        <v>52</v>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v>Wed Oct 11 2023 00:03:32 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G41" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H41" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>806128</v>
+      </c>
+      <c r="B42">
+        <v>1057</v>
+      </c>
+      <c r="C42" t="str">
+        <v/>
+      </c>
+      <c r="D42">
+        <v>72</v>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v>Wed Oct 11 2023 00:16:40 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G42" t="str">
+        <v>PayPal</v>
+      </c>
+      <c r="H42" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>806163</v>
+      </c>
+      <c r="B43">
+        <v>1057</v>
+      </c>
+      <c r="C43" t="str">
+        <v/>
+      </c>
+      <c r="D43">
+        <v>72</v>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v>Wed Oct 11 2023 00:52:30 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G43" t="str">
+        <v>PayPal</v>
+      </c>
+      <c r="H43" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>806181</v>
+      </c>
+      <c r="B44">
+        <v>1057</v>
+      </c>
+      <c r="C44" t="str">
+        <v/>
+      </c>
+      <c r="D44">
+        <v>500</v>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v>Wed Oct 11 2023 01:06:07 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G44" t="str">
+        <v>PayPal</v>
+      </c>
+      <c r="H44" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>806316</v>
+      </c>
+      <c r="B45">
+        <v>1057</v>
+      </c>
+      <c r="C45" t="str">
+        <v/>
+      </c>
+      <c r="D45">
+        <v>300</v>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v>Wed Oct 11 2023 03:25:01 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G45" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H45" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>806342</v>
+      </c>
+      <c r="B46">
+        <v>1057</v>
+      </c>
+      <c r="C46" t="str">
+        <v/>
+      </c>
+      <c r="D46">
+        <v>26</v>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v>Wed Oct 11 2023 03:47:28 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G46" t="str">
+        <v>PayPal</v>
+      </c>
+      <c r="H46" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>806602</v>
+      </c>
+      <c r="B47">
+        <v>1057</v>
+      </c>
+      <c r="C47" t="str">
+        <v/>
+      </c>
+      <c r="D47">
+        <v>72</v>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v>Wed Oct 11 2023 12:12:21 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G47" t="str">
+        <v>PayPal</v>
+      </c>
+      <c r="H47" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>806638</v>
+      </c>
+      <c r="B48">
+        <v>1057</v>
+      </c>
+      <c r="C48" t="str">
+        <v/>
+      </c>
+      <c r="D48">
+        <v>180</v>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v>Wed Oct 11 2023 13:11:24 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G48" t="str">
+        <v>PayPal</v>
+      </c>
+      <c r="H48" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>806703</v>
+      </c>
+      <c r="B49">
+        <v>1057</v>
+      </c>
+      <c r="C49" t="str">
+        <v/>
+      </c>
+      <c r="D49">
+        <v>72</v>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v>Wed Oct 11 2023 15:04:54 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G49" t="str">
+        <v>PayPal</v>
+      </c>
+      <c r="H49" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>806746</v>
+      </c>
+      <c r="B50">
+        <v>1057</v>
+      </c>
+      <c r="C50" t="str">
+        <v/>
+      </c>
+      <c r="D50">
+        <v>10</v>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v>Wed Oct 11 2023 15:40:52 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G50" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H50" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>806776</v>
+      </c>
+      <c r="B51">
+        <v>1057</v>
+      </c>
+      <c r="C51" t="str">
+        <v/>
+      </c>
+      <c r="D51">
+        <v>261</v>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v>Wed Oct 11 2023 16:10:57 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G51" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H51" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>806806</v>
+      </c>
+      <c r="B52">
+        <v>1057</v>
+      </c>
+      <c r="C52" t="str">
+        <v/>
+      </c>
+      <c r="D52">
+        <v>72</v>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v>Wed Oct 11 2023 16:31:13 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G52" t="str">
+        <v>PayPal</v>
+      </c>
+      <c r="H52" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>806827</v>
+      </c>
+      <c r="B53">
+        <v>1057</v>
+      </c>
+      <c r="C53" t="str">
+        <v/>
+      </c>
+      <c r="D53">
+        <v>52</v>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
+        <v>Wed Oct 11 2023 16:42:43 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G53" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H53" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>806843</v>
+      </c>
+      <c r="B54">
+        <v>1057</v>
+      </c>
+      <c r="C54" t="str">
+        <v/>
+      </c>
+      <c r="D54">
+        <v>216</v>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v>Wed Oct 11 2023 16:56:50 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G54" t="str">
+        <v>PayPal</v>
+      </c>
+      <c r="H54" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>806860</v>
+      </c>
+      <c r="B55">
+        <v>1057</v>
+      </c>
+      <c r="C55" t="str">
+        <v/>
+      </c>
+      <c r="D55">
+        <v>260</v>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v>Wed Oct 11 2023 17:18:39 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G55" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H55" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>806931</v>
+      </c>
+      <c r="B56">
+        <v>1057</v>
+      </c>
+      <c r="C56" t="str">
+        <v/>
+      </c>
+      <c r="D56">
+        <v>500</v>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v>Wed Oct 11 2023 18:47:28 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G56" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H56" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>806990</v>
+      </c>
+      <c r="B57">
+        <v>1057</v>
+      </c>
+      <c r="C57" t="str">
+        <v/>
+      </c>
+      <c r="D57">
+        <v>30</v>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v>Wed Oct 11 2023 19:58:24 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G57" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H57" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>807013</v>
+      </c>
+      <c r="B58">
+        <v>1057</v>
+      </c>
+      <c r="C58" t="str">
+        <v/>
+      </c>
+      <c r="D58">
+        <v>52</v>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v>Wed Oct 11 2023 20:33:29 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G58" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H58" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>807015</v>
+      </c>
+      <c r="B59">
+        <v>1057</v>
+      </c>
+      <c r="C59" t="str">
+        <v/>
+      </c>
+      <c r="D59">
+        <v>104</v>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v>Wed Oct 11 2023 20:35:28 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G59" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H59" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>807056</v>
+      </c>
+      <c r="B60">
+        <v>1057</v>
+      </c>
+      <c r="C60" t="str">
+        <v/>
+      </c>
+      <c r="D60">
+        <v>52</v>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v>Wed Oct 11 2023 21:24:47 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G60" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H60" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>807388</v>
+      </c>
+      <c r="B61">
+        <v>1057</v>
+      </c>
+      <c r="C61" t="str">
+        <v/>
+      </c>
+      <c r="D61">
+        <v>26</v>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v>Thu Oct 12 2023 01:34:10 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G61" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H61" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>807443</v>
+      </c>
+      <c r="B62">
+        <v>1057</v>
+      </c>
+      <c r="C62" t="str">
+        <v/>
+      </c>
+      <c r="D62">
+        <v>52</v>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
+        <v>Thu Oct 12 2023 02:34:53 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G62" t="str">
+        <v>PayPal</v>
+      </c>
+      <c r="H62" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>807858</v>
+      </c>
+      <c r="B63">
+        <v>1057</v>
+      </c>
+      <c r="C63" t="str">
+        <v/>
+      </c>
+      <c r="D63">
+        <v>126</v>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63" t="str">
+        <v>Thu Oct 12 2023 15:58:30 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G63" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H63" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>807902</v>
+      </c>
+      <c r="B64">
+        <v>1057</v>
+      </c>
+      <c r="C64" t="str">
+        <v/>
+      </c>
+      <c r="D64">
+        <v>52</v>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <v>Thu Oct 12 2023 17:02:54 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G64" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H64" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>807922</v>
+      </c>
+      <c r="B65">
+        <v>1057</v>
+      </c>
+      <c r="C65" t="str">
+        <v/>
+      </c>
+      <c r="D65">
+        <v>1000</v>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v>Thu Oct 12 2023 17:28:28 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G65" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H65" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>807957</v>
+      </c>
+      <c r="B66">
+        <v>1057</v>
+      </c>
+      <c r="C66" t="str">
+        <v/>
+      </c>
+      <c r="D66">
+        <v>150</v>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <v>Thu Oct 12 2023 18:04:23 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G66" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H66" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>808099</v>
+      </c>
+      <c r="B67">
+        <v>1057</v>
+      </c>
+      <c r="C67" t="str">
+        <v/>
+      </c>
+      <c r="D67">
+        <v>126</v>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <v>Thu Oct 12 2023 20:44:06 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G67" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H67" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>808692</v>
+      </c>
+      <c r="B68">
+        <v>1057</v>
+      </c>
+      <c r="C68" t="str">
+        <v/>
+      </c>
+      <c r="D68">
+        <v>26</v>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68" t="str">
+        <v>Fri Oct 13 2023 19:08:28 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G68" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H68" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>808760</v>
+      </c>
+      <c r="B69">
+        <v>1057</v>
+      </c>
+      <c r="C69" t="str">
+        <v/>
+      </c>
+      <c r="D69">
+        <v>52</v>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <v>Fri Oct 13 2023 21:43:31 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G69" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H69" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>808977</v>
+      </c>
+      <c r="B70">
+        <v>1057</v>
+      </c>
+      <c r="C70" t="str">
+        <v/>
+      </c>
+      <c r="D70">
+        <v>26</v>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <v>Sun Oct 15 2023 04:38:36 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G70" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H70" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>808996</v>
+      </c>
+      <c r="B71">
+        <v>1057</v>
+      </c>
+      <c r="C71" t="str">
+        <v/>
+      </c>
+      <c r="D71">
+        <v>126</v>
+      </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
+      <c r="F71" t="str">
+        <v>Sun Oct 15 2023 06:39:22 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G71" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H71" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>809158</v>
+      </c>
+      <c r="B72">
+        <v>1057</v>
+      </c>
+      <c r="C72" t="str">
+        <v/>
+      </c>
+      <c r="D72">
+        <v>126</v>
+      </c>
+      <c r="E72" t="str">
+        <v/>
+      </c>
+      <c r="F72" t="str">
+        <v>Sun Oct 15 2023 17:41:59 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G72" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H72" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>809727</v>
+      </c>
+      <c r="B73">
+        <v>1057</v>
+      </c>
+      <c r="C73" t="str">
+        <v/>
+      </c>
+      <c r="D73">
+        <v>200</v>
+      </c>
+      <c r="E73" t="str">
+        <v/>
+      </c>
+      <c r="F73" t="str">
+        <v>Mon Oct 16 2023 12:43:27 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G73" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H73" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>809969</v>
+      </c>
+      <c r="B74">
+        <v>1057</v>
+      </c>
+      <c r="C74" t="str">
+        <v/>
+      </c>
+      <c r="D74">
+        <v>72</v>
+      </c>
+      <c r="E74" t="str">
+        <v/>
+      </c>
+      <c r="F74" t="str">
+        <v>Mon Oct 16 2023 20:04:31 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G74" t="str">
+        <v>PayPal</v>
+      </c>
+      <c r="H74" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>809982</v>
+      </c>
+      <c r="B75">
+        <v>1057</v>
+      </c>
+      <c r="C75" t="str">
+        <v/>
+      </c>
+      <c r="D75">
+        <v>72</v>
+      </c>
+      <c r="E75" t="str">
+        <v/>
+      </c>
+      <c r="F75" t="str">
+        <v>Mon Oct 16 2023 20:28:30 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G75" t="str">
+        <v>PayPal</v>
+      </c>
+      <c r="H75" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>811543</v>
+      </c>
+      <c r="B76">
+        <v>1057</v>
+      </c>
+      <c r="C76" t="str">
+        <v/>
+      </c>
+      <c r="D76">
+        <v>26</v>
+      </c>
+      <c r="E76" t="str">
+        <v/>
+      </c>
+      <c r="F76" t="str">
+        <v>Wed Oct 18 2023 23:38:20 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G76" t="str">
+        <v>PayPal</v>
+      </c>
+      <c r="H76" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>812083</v>
+      </c>
+      <c r="B77">
+        <v>1057</v>
+      </c>
+      <c r="C77" t="str">
+        <v/>
+      </c>
+      <c r="D77">
+        <v>18</v>
+      </c>
+      <c r="E77" t="str">
+        <v/>
+      </c>
+      <c r="F77" t="str">
+        <v>Fri Oct 20 2023 09:31:39 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G77" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H77" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>812962</v>
+      </c>
+      <c r="B78">
+        <v>1057</v>
+      </c>
+      <c r="C78" t="str">
+        <v/>
+      </c>
+      <c r="D78">
+        <v>260</v>
+      </c>
+      <c r="E78" t="str">
+        <v/>
+      </c>
+      <c r="F78" t="str">
+        <v>Mon Oct 23 2023 17:23:46 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G78" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H78" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>817757</v>
+      </c>
+      <c r="B79">
+        <v>1057</v>
+      </c>
+      <c r="C79" t="str">
+        <v/>
+      </c>
+      <c r="D79">
+        <v>260</v>
+      </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+      <c r="F79" t="str">
+        <v>Sun Oct 29 2023 18:03:34 GMT+0200 (שעון ישראל (חורף))</v>
+      </c>
+      <c r="G79" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H79" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>825245</v>
+      </c>
+      <c r="B80">
+        <v>1057</v>
+      </c>
+      <c r="C80" t="str">
+        <v/>
+      </c>
+      <c r="D80">
+        <v>80</v>
+      </c>
+      <c r="E80" t="str">
+        <v/>
+      </c>
+      <c r="F80" t="str">
+        <v>Fri Nov 03 2023 13:11:55 GMT+0200 (שעון ישראל (חורף))</v>
+      </c>
+      <c r="G80" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H80" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>828696</v>
+      </c>
+      <c r="B81">
+        <v>1057</v>
+      </c>
+      <c r="C81" t="str">
+        <v/>
+      </c>
+      <c r="D81">
+        <v>72</v>
+      </c>
+      <c r="E81" t="str">
+        <v/>
+      </c>
+      <c r="F81" t="str">
+        <v>Mon Nov 06 2023 20:47:04 GMT+0200 (שעון ישראל (חורף))</v>
+      </c>
+      <c r="G81" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H81" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>1268040</v>
+      </c>
+      <c r="B82">
+        <v>1</v>
+      </c>
+      <c r="C82" t="str">
+        <v/>
+      </c>
+      <c r="D82">
+        <v>80</v>
+      </c>
+      <c r="E82" t="str">
+        <v/>
+      </c>
+      <c r="F82" t="str">
+        <v>Sun May 04 2025 13:05:43 GMT+0300 (שעון ישראל (קיץ))</v>
+      </c>
+      <c r="G82" t="str">
+        <v>CreditCard</v>
+      </c>
+      <c r="H82" t="str">
+        <v>project-unresolved</v>
+      </c>
+      <c r="I82">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J24"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I82"/>
   </ignoredErrors>
 </worksheet>
 </file>